--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-20).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-20).xlsx
@@ -935,22 +935,22 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 8.908,27</t>
-  </si>
-  <si>
-    <t>96.7</t>
-  </si>
-  <si>
-    <t>62.0</t>
-  </si>
-  <si>
-    <t>6.36</t>
-  </si>
-  <si>
-    <t>21.3</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 8.894,50</t>
+  </si>
+  <si>
+    <t>96.6</t>
+  </si>
+  <si>
+    <t>61.8</t>
+  </si>
+  <si>
+    <t>6.33</t>
+  </si>
+  <si>
+    <t>21.2</t>
   </si>
   <si>
     <t>8.2</t>
@@ -959,7 +959,7 @@
     <t>6.0</t>
   </si>
   <si>
-    <t>33.9%</t>
+    <t>34.4%</t>
   </si>
   <si>
     <t>17.0%</t>
@@ -980,16 +980,16 @@
     <t>6.7%</t>
   </si>
   <si>
-    <t>2.3%</t>
+    <t>2.4%</t>
   </si>
   <si>
     <t>4.6%</t>
   </si>
   <si>
-    <t>2241.0</t>
-  </si>
-  <si>
-    <t>1874.0</t>
+    <t>2244.0</t>
+  </si>
+  <si>
+    <t>1877.0</t>
   </si>
   <si>
     <t>136.0</t>
@@ -998,7 +998,7 @@
     <t>57.0</t>
   </si>
   <si>
-    <t>376.0</t>
+    <t>377.0</t>
   </si>
   <si>
     <t>130.0</t>
@@ -1007,10 +1007,10 @@
     <t>30.0</t>
   </si>
   <si>
-    <t>738.0</t>
-  </si>
-  <si>
-    <t>259.0</t>
+    <t>739.0</t>
+  </si>
+  <si>
+    <t>260.0</t>
   </si>
   <si>
     <t>509.0</t>
@@ -12630,7 +12630,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12658,14 +12658,26 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
+      <c r="M76" s="5">
+        <v>8665.1100000000006</v>
+      </c>
+      <c r="N76" s="6">
+        <v>111</v>
+      </c>
       <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
+      <c r="P76" s="7">
+        <v>2.9853798245614036</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>15.71979125</v>
+      </c>
+      <c r="R76" s="8">
+        <v>5.4186863636363638</v>
+      </c>
       <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
+      <c r="T76" s="9">
+        <v>0.53749999999999998</v>
+      </c>
       <c r="U76" s="9"/>
       <c r="V76" s="9"/>
       <c r="W76" s="9"/>
@@ -26840,7 +26852,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>51</v>
@@ -26870,35 +26882,93 @@
         <v>58</v>
       </c>
       <c r="L172" s="4"/>
-      <c r="M172" s="5"/>
-      <c r="N172" s="6"/>
-      <c r="O172" s="6"/>
-      <c r="P172" s="7"/>
-      <c r="Q172" s="8"/>
-      <c r="R172" s="8"/>
-      <c r="S172" s="8"/>
-      <c r="T172" s="9"/>
-      <c r="U172" s="9"/>
-      <c r="V172" s="9"/>
-      <c r="W172" s="9"/>
-      <c r="X172" s="9"/>
-      <c r="Y172" s="9"/>
-      <c r="Z172" s="9"/>
-      <c r="AA172" s="9"/>
-      <c r="AB172" s="9"/>
-      <c r="AC172" s="9"/>
-      <c r="AD172" s="6"/>
-      <c r="AE172" s="6"/>
-      <c r="AF172" s="6"/>
-      <c r="AG172" s="6"/>
-      <c r="AH172" s="6"/>
-      <c r="AI172" s="6"/>
-      <c r="AJ172" s="6"/>
-      <c r="AK172" s="6"/>
-      <c r="AL172" s="6"/>
-      <c r="AM172" s="6"/>
-      <c r="AN172" s="9"/>
-      <c r="AO172" s="6"/>
+      <c r="M172" s="5">
+        <v>3205.3000000000002</v>
+      </c>
+      <c r="N172" s="6">
+        <v>41</v>
+      </c>
+      <c r="O172" s="6">
+        <v>29</v>
+      </c>
+      <c r="P172" s="7">
+        <v>4.3780487804878048</v>
+      </c>
+      <c r="Q172" s="8">
+        <v>15.160344827586206</v>
+      </c>
+      <c r="R172" s="8">
+        <v>3.9362068965517243</v>
+      </c>
+      <c r="S172" s="8">
+        <v>7</v>
+      </c>
+      <c r="T172" s="9">
+        <v>0.58620689655172409</v>
+      </c>
+      <c r="U172" s="9">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="V172" s="9">
+        <v>0</v>
+      </c>
+      <c r="W172" s="9">
+        <v>0</v>
+      </c>
+      <c r="X172" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y172" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AB172" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AC172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD172" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO172" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP172" s="4">
         <v>58</v>
       </c>
@@ -30279,7 +30349,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30309,14 +30379,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>12335.33</v>
+      </c>
+      <c r="N195" s="6">
+        <v>134</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>4.6276083969465649</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>22.3825</v>
+      </c>
+      <c r="R195" s="8">
+        <v>10.760999999999999</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.080000000000000002</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-20).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-20).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 8.894,50</t>
-  </si>
-  <si>
-    <t>96.6</t>
-  </si>
-  <si>
-    <t>61.8</t>
-  </si>
-  <si>
-    <t>6.33</t>
-  </si>
-  <si>
-    <t>21.2</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 8.903,98</t>
+  </si>
+  <si>
+    <t>96.8</t>
+  </si>
+  <si>
+    <t>62.3</t>
+  </si>
+  <si>
+    <t>6.42</t>
+  </si>
+  <si>
+    <t>21.4</t>
   </si>
   <si>
     <t>8.2</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>34.4%</t>
-  </si>
-  <si>
-    <t>17.0%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>33.8%</t>
+  </si>
+  <si>
+    <t>17.1%</t>
   </si>
   <si>
     <t>1.2%</t>
@@ -980,46 +980,46 @@
     <t>6.7%</t>
   </si>
   <si>
-    <t>2.4%</t>
-  </si>
-  <si>
-    <t>4.6%</t>
-  </si>
-  <si>
-    <t>2244.0</t>
-  </si>
-  <si>
-    <t>1877.0</t>
-  </si>
-  <si>
-    <t>136.0</t>
-  </si>
-  <si>
-    <t>57.0</t>
-  </si>
-  <si>
-    <t>377.0</t>
-  </si>
-  <si>
-    <t>130.0</t>
-  </si>
-  <si>
-    <t>30.0</t>
-  </si>
-  <si>
-    <t>739.0</t>
-  </si>
-  <si>
-    <t>260.0</t>
-  </si>
-  <si>
-    <t>509.0</t>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>4.7%</t>
+  </si>
+  <si>
+    <t>2325.0</t>
+  </si>
+  <si>
+    <t>1948.0</t>
+  </si>
+  <si>
+    <t>139.0</t>
+  </si>
+  <si>
+    <t>59.0</t>
+  </si>
+  <si>
+    <t>382.0</t>
+  </si>
+  <si>
+    <t>132.0</t>
+  </si>
+  <si>
+    <t>33.0</t>
+  </si>
+  <si>
+    <t>766.0</t>
+  </si>
+  <si>
+    <t>266.0</t>
+  </si>
+  <si>
+    <t>534.0</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>63.0</t>
+    <t>73.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3239,7 +3239,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3269,35 +3269,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>9804.9599999999991</v>
+      </c>
+      <c r="N13" s="6">
+        <v>113</v>
+      </c>
+      <c r="O13" s="6">
+        <v>91</v>
+      </c>
+      <c r="P13" s="7">
+        <v>26.487262601626018</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>53.51391978021978</v>
+      </c>
+      <c r="R13" s="8">
+        <v>16.371852222222223</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.12087912087912088</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.2967032967032967</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0.010989010989</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.01098901098901099</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>29</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>27</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>14</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.10989010989010989</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>10</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -9996,7 +10054,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10026,35 +10084,93 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="M58" s="5">
+        <v>9738.0300000000007</v>
+      </c>
+      <c r="N58" s="6">
+        <v>115</v>
+      </c>
+      <c r="O58" s="6">
+        <v>83</v>
+      </c>
+      <c r="P58" s="7">
+        <v>4.1070567567567569</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>16.523695180722893</v>
+      </c>
+      <c r="R58" s="8">
+        <v>5.2524096385542167</v>
+      </c>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
+      <c r="T58" s="9">
+        <v>0.42168674698795183</v>
+      </c>
+      <c r="U58" s="9">
+        <v>0.072289156626506021</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.012048192771084338</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0.012048192770999999</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.012048192771084338</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0.024096385542168676</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.024096385542168676</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -12664,7 +12780,9 @@
       <c r="N76" s="6">
         <v>111</v>
       </c>
-      <c r="O76" s="6"/>
+      <c r="O76" s="6">
+        <v>80</v>
+      </c>
       <c r="P76" s="7">
         <v>2.9853798245614036</v>
       </c>
@@ -12674,31 +12792,75 @@
       <c r="R76" s="8">
         <v>5.4186863636363638</v>
       </c>
-      <c r="S76" s="8"/>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
       <c r="T76" s="9">
         <v>0.53749999999999998</v>
       </c>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="U76" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.037499999999999999</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.1125</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>43</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>35</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>23</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>9</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -27981,7 +28143,9 @@
       <c r="N179" s="6">
         <v>148</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>85</v>
+      </c>
       <c r="P179" s="7">
         <v>8.7793376712328772</v>
       </c>
@@ -27991,31 +28155,75 @@
       <c r="R179" s="8">
         <v>1.6966273809523809</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.45882352941176469</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.035294117647058823</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0.011764705882352941</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0.023529411764705882</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
